--- a/paper/tables/tables.xlsx
+++ b/paper/tables/tables.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Colby\Documents\GitHub\peleke\paper\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE20CB58-AEE1-496D-B9A0-A740FC8AE89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48EAAB7-212F-478D-B6FC-5183A65E48BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{74FBB4F4-0BB2-49E8-8273-9D963BDE2F1A}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{74FBB4F4-0BB2-49E8-8273-9D963BDE2F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Training Data" sheetId="1" r:id="rId1"/>
     <sheet name="Models" sheetId="2" r:id="rId2"/>
-    <sheet name="VDW_Hits" sheetId="3" r:id="rId3"/>
-    <sheet name="VDW_Hits (RAW)" sheetId="4" r:id="rId4"/>
+    <sheet name="VDW_Hits - ESM3" sheetId="3" r:id="rId3"/>
+    <sheet name="VDW_Hits - ESM3 (RAW)" sheetId="4" r:id="rId4"/>
+    <sheet name="VDW Hits - Boltz-2" sheetId="6" r:id="rId5"/>
+    <sheet name="VDW Hits - Boltz-2 (RAW)" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
   <si>
     <t>pdb_id</t>
   </si>
@@ -326,13 +328,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -965,24 +967,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -990,16 +992,16 @@
       <c r="A3" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B2, 2),"% (", ROUND('VDW_Hits (RAW)'!E2,2), ")")</f>
+      <c r="B3" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B2, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E2,2), ")")</f>
         <v>22.73% (63.34)</v>
       </c>
-      <c r="C3" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C2, 2),"% (", ROUND('VDW_Hits (RAW)'!F2,2), ")")</f>
+      <c r="C3" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C2, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F2,2), ")")</f>
         <v>15% (106.84)</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D2, 2),"% (", ROUND('VDW_Hits (RAW)'!G2,2), ")")</f>
+      <c r="D3" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D2, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G2,2), ")")</f>
         <v>18.42% (49.88)</v>
       </c>
     </row>
@@ -1007,16 +1009,16 @@
       <c r="A4" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B3, 2),"% (", ROUND('VDW_Hits (RAW)'!E3,2), ")")</f>
+      <c r="B4" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B3, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E3,2), ")")</f>
         <v>2.63% (218.86)</v>
       </c>
-      <c r="C4" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C3, 2),"% (", ROUND('VDW_Hits (RAW)'!F3,2), ")")</f>
+      <c r="C4" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C3, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F3,2), ")")</f>
         <v>10.81% (289.61)</v>
       </c>
-      <c r="D4" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D3, 2),"% (", ROUND('VDW_Hits (RAW)'!G3,2), ")")</f>
+      <c r="D4" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D3, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G3,2), ")")</f>
         <v>9.3% (131.62)</v>
       </c>
     </row>
@@ -1024,16 +1026,16 @@
       <c r="A5" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B4, 2),"% (", ROUND('VDW_Hits (RAW)'!E4,2), ")")</f>
+      <c r="B5" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B4, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E4,2), ")")</f>
         <v>20% (101.64)</v>
       </c>
-      <c r="C5" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C4, 2),"% (", ROUND('VDW_Hits (RAW)'!F4,2), ")")</f>
+      <c r="C5" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C4, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F4,2), ")")</f>
         <v>23.26% (24.66)</v>
       </c>
-      <c r="D5" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D4, 2),"% (", ROUND('VDW_Hits (RAW)'!G4,2), ")")</f>
+      <c r="D5" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D4, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G4,2), ")")</f>
         <v>20% (163.88)</v>
       </c>
     </row>
@@ -1041,16 +1043,16 @@
       <c r="A6" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B5, 2),"% (", ROUND('VDW_Hits (RAW)'!E5,2), ")")</f>
+      <c r="B6" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B5, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E5,2), ")")</f>
         <v>36.17% (-3.46)</v>
       </c>
-      <c r="C6" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C5, 2),"% (", ROUND('VDW_Hits (RAW)'!F5,2), ")")</f>
+      <c r="C6" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C5, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F5,2), ")")</f>
         <v>46.81% (-10.11)</v>
       </c>
-      <c r="D6" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D5, 2),"% (", ROUND('VDW_Hits (RAW)'!G5,2), ")")</f>
+      <c r="D6" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D5, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G5,2), ")")</f>
         <v>31.91% (13.64)</v>
       </c>
     </row>
@@ -1058,16 +1060,16 @@
       <c r="A7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B6, 2),"% (", ROUND('VDW_Hits (RAW)'!E6,2), ")")</f>
+      <c r="B7" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B6, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E6,2), ")")</f>
         <v>67.39% (-52.56)</v>
       </c>
-      <c r="C7" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C6, 2),"% (", ROUND('VDW_Hits (RAW)'!F6,2), ")")</f>
+      <c r="C7" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C6, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F6,2), ")")</f>
         <v>57.78% (-52.52)</v>
       </c>
-      <c r="D7" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D6, 2),"% (", ROUND('VDW_Hits (RAW)'!G6,2), ")")</f>
+      <c r="D7" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D6, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G6,2), ")")</f>
         <v>69.39% (-57.98)</v>
       </c>
     </row>
@@ -1075,16 +1077,16 @@
       <c r="A8" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B7, 2),"% (", ROUND('VDW_Hits (RAW)'!E7,2), ")")</f>
+      <c r="B8" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B7, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E7,2), ")")</f>
         <v>73.47% (-66.72)</v>
       </c>
-      <c r="C8" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C7, 2),"% (", ROUND('VDW_Hits (RAW)'!F7,2), ")")</f>
+      <c r="C8" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C7, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F7,2), ")")</f>
         <v>79.59% (-82.51)</v>
       </c>
-      <c r="D8" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D7, 2),"% (", ROUND('VDW_Hits (RAW)'!G7,2), ")")</f>
+      <c r="D8" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D7, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G7,2), ")")</f>
         <v>76.6% (-70.12)</v>
       </c>
     </row>
@@ -1092,16 +1094,16 @@
       <c r="A9" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!B8, 2),"% (", ROUND('VDW_Hits (RAW)'!E8,2), ")")</f>
+      <c r="B9" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!B8, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!E8,2), ")")</f>
         <v>79.59% (-71.53)</v>
       </c>
-      <c r="C9" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!C8, 2),"% (", ROUND('VDW_Hits (RAW)'!F8,2), ")")</f>
+      <c r="C9" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!C8, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!F8,2), ")")</f>
         <v>70.83% (-62.52)</v>
       </c>
-      <c r="D9" s="6" t="str">
-        <f>_xlfn.CONCAT(ROUND('VDW_Hits (RAW)'!D8, 2),"% (", ROUND('VDW_Hits (RAW)'!G8,2), ")")</f>
+      <c r="D9" s="4" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW_Hits - ESM3 (RAW)'!D8, 2),"% (", ROUND('VDW_Hits - ESM3 (RAW)'!G8,2), ")")</f>
         <v>72.92% (-73.38)</v>
       </c>
     </row>
@@ -1155,22 +1157,22 @@
       <c r="A2" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <v>22.727273</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>15</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>18.421053000000001</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>63.343150000000001</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <v>106.839</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>49.881549999999997</v>
       </c>
     </row>
@@ -1178,22 +1180,22 @@
       <c r="A3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>2.6315789999999999</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>10.81081</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>9.3023260000000008</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>218.85599999999999</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>289.61399999999998</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>131.61600000000001</v>
       </c>
     </row>
@@ -1201,22 +1203,22 @@
       <c r="A4" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>20</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>23.25581</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>20</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>101.6448</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>24.6556</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>163.881</v>
       </c>
     </row>
@@ -1224,22 +1226,22 @@
       <c r="A5" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>36.170212999999997</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>46.808509999999998</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>31.914894</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>-3.4557799999999999</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>-10.110799999999999</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>13.6427</v>
       </c>
     </row>
@@ -1247,22 +1249,22 @@
       <c r="A6" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>67.391304000000005</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>57.77778</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>69.387754999999999</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>-52.559049999999999</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>-52.519399999999997</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>-57.981499999999997</v>
       </c>
     </row>
@@ -1270,22 +1272,22 @@
       <c r="A7" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>73.469387999999995</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>79.591840000000005</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>76.595744999999994</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>-66.719499999999996</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>-82.513800000000003</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>-70.123900000000006</v>
       </c>
     </row>
@@ -1293,23 +1295,387 @@
       <c r="A8" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>79.591836999999998</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>70.833330000000004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>72.916667000000004</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>-71.534400000000005</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>-62.515549999999998</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>-73.379649999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A490AD00-BA37-4BA5-A4A1-E8630A0DF635}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B2,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E2,2),")")</f>
+        <v>69.39% (-38.89)</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C2,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F2,2),")")</f>
+        <v>73.47% (-40.71)</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D2,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G2,2),")")</f>
+        <v>71.43% (-45.84)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B3,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E3,2),")")</f>
+        <v>72% (-46.28)</v>
+      </c>
+      <c r="C4" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C3,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F3,2),")")</f>
+        <v>80% (-44.62)</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D3,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G3,2),")")</f>
+        <v>70% (-36.11)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B4,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E4,2),")")</f>
+        <v>50% (-29.85)</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C4,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F4,2),")")</f>
+        <v>43.48% (-27.75)</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D4,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G4,2),")")</f>
+        <v>24.44% (-15.89)</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B5,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E5,2),")")</f>
+        <v>71.43% (-46.02)</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C5,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F5,2),")")</f>
+        <v>87.76% (-49.1)</v>
+      </c>
+      <c r="D6" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D5,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G5,2),")")</f>
+        <v>81.25% (-47.44)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B6,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E6,2),")")</f>
+        <v>76.09% (-44.36)</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C6,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F6,2),")")</f>
+        <v>80% (-41.13)</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D6,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G6,2),")")</f>
+        <v>73.47% (-50.75)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B7,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E7,2),")")</f>
+        <v>76% (-41.37)</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C7,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F7,2),")")</f>
+        <v>74% (-39.6)</v>
+      </c>
+      <c r="D8" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D7,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G7,2),")")</f>
+        <v>84% (-40.74)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!B8,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!E8,2),")")</f>
+        <v>80% (-46.02)</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!C8,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!F8,2),")")</f>
+        <v>82% (-45.27)</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <f>_xlfn.CONCAT(ROUND('VDW Hits - Boltz-2 (RAW)'!D8,2), "% (",ROUND('VDW Hits - Boltz-2 (RAW)'!G8,2),")")</f>
+        <v>73.47% (-45.73)</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D208EC-3654-4D28-9324-F40EB28FDE41}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>69.38776</v>
+      </c>
+      <c r="C2">
+        <v>73.469390000000004</v>
+      </c>
+      <c r="D2">
+        <v>71.428569999999993</v>
+      </c>
+      <c r="E2">
+        <v>-38.886600000000001</v>
+      </c>
+      <c r="F2">
+        <v>-40.707500000000003</v>
+      </c>
+      <c r="G2">
+        <v>-45.8429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3">
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>-46.277500000000003</v>
+      </c>
+      <c r="F3">
+        <v>-44.6205</v>
+      </c>
+      <c r="G3">
+        <v>-36.112949999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>43.478259999999999</v>
+      </c>
+      <c r="D4">
+        <v>24.44444</v>
+      </c>
+      <c r="E4">
+        <v>-29.8504</v>
+      </c>
+      <c r="F4">
+        <v>-27.751349999999999</v>
+      </c>
+      <c r="G4">
+        <v>-15.8887</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5">
+        <v>71.428569999999993</v>
+      </c>
+      <c r="C5">
+        <v>87.755099999999999</v>
+      </c>
+      <c r="D5">
+        <v>81.25</v>
+      </c>
+      <c r="E5">
+        <v>-46.0182</v>
+      </c>
+      <c r="F5">
+        <v>-49.098399999999998</v>
+      </c>
+      <c r="G5">
+        <v>-47.435850000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6">
+        <v>76.086960000000005</v>
+      </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>73.469390000000004</v>
+      </c>
+      <c r="E6">
+        <v>-44.360250000000001</v>
+      </c>
+      <c r="F6">
+        <v>-41.130249999999997</v>
+      </c>
+      <c r="G6">
+        <v>-50.753900000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7">
+        <v>76</v>
+      </c>
+      <c r="C7">
+        <v>74</v>
+      </c>
+      <c r="D7">
+        <v>84</v>
+      </c>
+      <c r="E7">
+        <v>-41.366050000000001</v>
+      </c>
+      <c r="F7">
+        <v>-39.600050000000003</v>
+      </c>
+      <c r="G7">
+        <v>-40.74165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="C8">
+        <v>82</v>
+      </c>
+      <c r="D8">
+        <v>73.469390000000004</v>
+      </c>
+      <c r="E8">
+        <v>-46.017249999999997</v>
+      </c>
+      <c r="F8">
+        <v>-45.268900000000002</v>
+      </c>
+      <c r="G8">
+        <v>-45.733499999999999</v>
       </c>
     </row>
   </sheetData>
